--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,782 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128223664</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91365</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>378828</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6745227</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128223665</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>378703</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6745016</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128223657</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80133</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>378778</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6745113</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128223659</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79053</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>378785</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6745189</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128223669</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92641</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>378774</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6745163</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128223668</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92641</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>378698</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6745029</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128223662</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78787</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>378778</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6745172</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128223660</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80132</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>378777</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6745092</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128223664</v>
       </c>
       <c r="B4" t="n">
-        <v>91365</v>
+        <v>91366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128223669</v>
       </c>
       <c r="B8" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128223668</v>
       </c>
       <c r="B9" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128223664</v>
       </c>
       <c r="B4" t="n">
-        <v>91366</v>
+        <v>91374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128223665</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128223657</v>
       </c>
       <c r="B6" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128223659</v>
       </c>
       <c r="B7" t="n">
-        <v>79053</v>
+        <v>79056</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128223669</v>
       </c>
       <c r="B8" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128223668</v>
       </c>
       <c r="B9" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128223662</v>
       </c>
       <c r="B10" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128223660</v>
       </c>
       <c r="B11" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128223664</v>
       </c>
       <c r="B4" t="n">
-        <v>91374</v>
+        <v>91466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128223665</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128223657</v>
       </c>
       <c r="B6" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128223659</v>
       </c>
       <c r="B7" t="n">
-        <v>79056</v>
+        <v>79107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128223669</v>
       </c>
       <c r="B8" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128223668</v>
       </c>
       <c r="B9" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128223662</v>
       </c>
       <c r="B10" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128223660</v>
       </c>
       <c r="B11" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128223664</v>
       </c>
       <c r="B4" t="n">
-        <v>91466</v>
+        <v>91478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128223665</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128223657</v>
       </c>
       <c r="B6" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128223659</v>
       </c>
       <c r="B7" t="n">
-        <v>79107</v>
+        <v>79111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128223669</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128223668</v>
       </c>
       <c r="B9" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128223662</v>
       </c>
       <c r="B10" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128223660</v>
       </c>
       <c r="B11" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128223664</v>
       </c>
       <c r="B4" t="n">
-        <v>91478</v>
+        <v>91480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128223665</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128223657</v>
       </c>
       <c r="B6" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128223659</v>
       </c>
       <c r="B7" t="n">
-        <v>79111</v>
+        <v>79113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128223669</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128223668</v>
       </c>
       <c r="B9" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128223662</v>
       </c>
       <c r="B10" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128223660</v>
       </c>
       <c r="B11" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128223664</v>
       </c>
       <c r="B4" t="n">
-        <v>91480</v>
+        <v>91481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128223669</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128223668</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128223664</v>
       </c>
       <c r="B4" t="n">
-        <v>91481</v>
+        <v>91508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128223665</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128223657</v>
       </c>
       <c r="B6" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128223659</v>
       </c>
       <c r="B7" t="n">
-        <v>79113</v>
+        <v>79140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128223669</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128223668</v>
       </c>
       <c r="B9" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128223662</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128223660</v>
       </c>
       <c r="B11" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128223664</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>91518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128223665</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128223657</v>
       </c>
       <c r="B6" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128223659</v>
       </c>
       <c r="B7" t="n">
-        <v>79140</v>
+        <v>79144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128223669</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>128223668</v>
       </c>
       <c r="B9" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>128223662</v>
       </c>
       <c r="B10" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>128223660</v>
       </c>
       <c r="B11" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74111081</v>
+        <v>128223664</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellanmyren, Vrm</t>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>378522.1873016638</v>
+        <v>378828</v>
       </c>
       <c r="R2" t="n">
-        <v>6744938.924371907</v>
+        <v>6745227</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-11-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-11-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74111080</v>
+        <v>128223657</v>
       </c>
       <c r="B3" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellanmyren, Vrm</t>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>378522.1873016638</v>
+        <v>378778</v>
       </c>
       <c r="R3" t="n">
-        <v>6744938.924371907</v>
+        <v>6745113</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-11-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-11-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128223664</v>
+        <v>128223668</v>
       </c>
       <c r="B4" t="n">
-        <v>91518</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>378828</v>
+        <v>378698</v>
       </c>
       <c r="R4" t="n">
-        <v>6745227</v>
+        <v>6745029</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128223665</v>
+        <v>128223669</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>378703</v>
+        <v>378774</v>
       </c>
       <c r="R5" t="n">
-        <v>6745016</v>
+        <v>6745163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128223657</v>
+        <v>128223670</v>
       </c>
       <c r="B6" t="n">
-        <v>80226</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>378778</v>
+        <v>378875</v>
       </c>
       <c r="R6" t="n">
-        <v>6745113</v>
+        <v>6745217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128223659</v>
+        <v>128223665</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>378785</v>
+        <v>378703</v>
       </c>
       <c r="R7" t="n">
-        <v>6745189</v>
+        <v>6745016</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128223669</v>
+        <v>128223667</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>378774</v>
+        <v>378905</v>
       </c>
       <c r="R8" t="n">
-        <v>6745163</v>
+        <v>6745266</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128223668</v>
+        <v>128223659</v>
       </c>
       <c r="B9" t="n">
-        <v>92794</v>
+        <v>79351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1419,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>378698</v>
+        <v>378785</v>
       </c>
       <c r="R9" t="n">
-        <v>6745029</v>
+        <v>6745189</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128223662</v>
+        <v>128223661</v>
       </c>
       <c r="B10" t="n">
-        <v>78877</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>378778</v>
+        <v>378845</v>
       </c>
       <c r="R10" t="n">
-        <v>6745172</v>
+        <v>6745102</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128223660</v>
+        <v>128223662</v>
       </c>
       <c r="B11" t="n">
-        <v>80225</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>378777</v>
+        <v>378778</v>
       </c>
       <c r="R11" t="n">
-        <v>6745092</v>
+        <v>6745172</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,6 +1642,597 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128223663</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>378889</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6745276</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128223658</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>378922</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6745277</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1963097</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>800 m V Stormyren (13C9g37), Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>378657</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6745068</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2002-06-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2002-06-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>130296371 / LOB PULM / Enstaka-sparsam (1)  / OBJ.AREA:0,7 ha</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Björn Ehrenroth</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>74111081</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mellanmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>378522</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6744939</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128223660</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SÖ om Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>378777</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6745092</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>74111080</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mellanmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>378522</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6744939</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41096-2025 artfynd.xlsx
+++ b/artfynd/A 41096-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223657</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223668</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223669</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223665</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223659</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223662</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1963097</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74111081</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223660</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74111080</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223664</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223670</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223667</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2039,6 +2109,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223661</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2136,6 +2211,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223663</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2233,8 +2313,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128223658</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>